--- a/data/trans_orig/IP1013-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1013-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>87638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174498</t>
+          <t>174476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>170925</t>
+          <t>171206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154319</t>
+          <t>154758</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>327622</t>
+          <t>327635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>676593</t>
+          <t>677199</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>718604</t>
+          <t>718603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1397700</t>
+          <t>1397180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80019</t>
+          <t>80418</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172004</t>
+          <t>171784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>445365</t>
+          <t>445109</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487676</t>
+          <t>487088</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>935732</t>
+          <t>934757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>941374</t>
+          <t>941414</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,93%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>162391</t>
+          <t>162013</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>333155</t>
+          <t>333591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>701128</t>
+          <t>701139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>706269</t>
+          <t>706272</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>741609</t>
+          <t>741833</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>746881</t>
+          <t>746876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1445642</t>
+          <t>1446298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1452984</t>
+          <t>1452488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467628</t>
+          <t>467911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>956616</t>
+          <t>956104</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168428</t>
+          <t>169199</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356632</t>
+          <t>355509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4967,54 +4967,54 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5993</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5306</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>699065</t>
+          <t>698378</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>704371</t>
+          <t>703774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,39 +5095,39 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1443483</t>
+          <t>1443560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP1013-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1013-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3229</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3207</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3236</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90225</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87638</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>86966</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>265</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174476</t>
+          <t>174505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1178,47 +1178,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,102 +1413,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3383</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2860</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3149</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3380</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4538</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4570</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157465</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154755</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>173444</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>171206</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>170917</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157465</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>154758</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,86%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>488</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>327635</t>
+          <t>327667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1264</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3822</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4443</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3371</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>721301</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>718598</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>679757</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>677199</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>676578</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1084</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>721301</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>718603</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2100</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1397180</t>
+          <t>1397197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1402373</t>
+          <t>1402374</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,107 +2325,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>624</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3119</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4242</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3641</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82913</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80427</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>82913</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>249</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171784</t>
+          <t>171183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2673,67 +2673,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4748</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1415</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4591</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4951</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1355</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5316</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>491049</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>487656</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>448285</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>445109</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>444749</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,69%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,9%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>491049</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>487088</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1352</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>934757</t>
+          <t>935322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>941414</t>
+          <t>941376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,107 +3011,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3327</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3722</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3310</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>164679</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>162013</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>162038</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,6%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>476</t>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>333591</t>
+          <t>333179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3359,67 +3359,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5270</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2076</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5789</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5725</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5668</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -3467,74 +3467,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>745522</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>742231</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>746879</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>704852</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>701139</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>706272</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>701203</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>706268</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>745522</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>741833</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>746876</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2077</t>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1446298</t>
+          <t>1445571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1452488</t>
+          <t>1453012</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4041,47 +4041,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,107 +4271,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1368</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4379</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4472</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4416</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1368</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4921</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -4384,74 +4384,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>470922</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>467911</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>467818</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1407</t>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>956104</t>
+          <t>956609</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,107 +4614,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3504</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3498</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3544</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4688</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -4727,74 +4727,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>171998</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>169199</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>169205</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,59%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>97,97%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>528</t>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355509</t>
+          <t>356653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5993</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6099</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -5070,74 +5070,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>702297</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>698378</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>698272</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>703774</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2123</t>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1443560</t>
+          <t>1443340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1448618</t>
+          <t>1448619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
